--- a/docs/iLa_SJ2526_Kurse-B1.xlsx
+++ b/docs/iLa_SJ2526_Kurse-B1.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10726"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Guido/IdeaProjects/ila-backend/docs/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/guido/IdeaProjects/ila-backend/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB50CA48-DFCC-7A47-83EE-765420ABB145}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1744D4A-8179-184E-8712-B7897F9A2A35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="680" windowWidth="28800" windowHeight="16680" xr2:uid="{FD870803-716F-F345-959C-C617E5CA4E3D}"/>
   </bookViews>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1311" uniqueCount="659">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1316" uniqueCount="660">
   <si>
     <t>Nachname</t>
   </si>
@@ -2264,6 +2264,9 @@
   </si>
   <si>
     <t>In typografischen Experimenten findest du heraus, wie sich Buchstaben und Schriften auf vielfältige Weise erzeugen oder entdecken lassen</t>
+  </si>
+  <si>
+    <t>6, 7</t>
   </si>
 </sst>
 </file>
@@ -2373,7 +2376,6 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -2386,6 +2388,7 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -2412,23 +2415,20 @@
     </dxf>
     <dxf>
       <font>
+        <b val="0"/>
+        <i val="0"/>
         <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="12"/>
+        <color theme="1"/>
         <name val="Aptos Narrow"/>
         <scheme val="minor"/>
       </font>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -2441,13 +2441,67 @@
         <name val="Aptos Narrow"/>
         <scheme val="minor"/>
       </font>
-      <numFmt numFmtId="30" formatCode="@"/>
+      <numFmt numFmtId="0" formatCode="General"/>
       <fill>
         <patternFill patternType="none">
           <fgColor indexed="64"/>
           <bgColor auto="1"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="h:mm;@"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <name val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="h:mm;@"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </font>
     </dxf>
     <dxf>
       <font>
@@ -2502,178 +2556,13 @@
         <name val="Aptos Narrow"/>
         <scheme val="minor"/>
       </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="h:mm;@"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <scheme val="minor"/>
-      </font>
       <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color auto="1"/>
-        <name val="Aptos Narrow"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <scheme val="minor"/>
-      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
@@ -2713,6 +2602,24 @@
     </dxf>
     <dxf>
       <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <font>
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
@@ -2722,13 +2629,50 @@
         <name val="Aptos Narrow"/>
         <scheme val="minor"/>
       </font>
-      <numFmt numFmtId="164" formatCode="h:mm;@"/>
+      <numFmt numFmtId="30" formatCode="@"/>
       <fill>
         <patternFill patternType="none">
           <fgColor indexed="64"/>
           <bgColor auto="1"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <name val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </font>
     </dxf>
     <dxf>
       <font>
@@ -2765,13 +2709,6 @@
         <name val="Aptos Narrow"/>
         <scheme val="minor"/>
       </font>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
     </dxf>
     <dxf>
       <font>
@@ -2794,6 +2731,23 @@
     </dxf>
     <dxf>
       <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
@@ -2813,22 +2767,20 @@
     </dxf>
     <dxf>
       <font>
+        <b val="0"/>
+        <i val="0"/>
         <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="12"/>
+        <color auto="1"/>
         <name val="Aptos Narrow"/>
         <scheme val="minor"/>
       </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
     </dxf>
     <dxf>
       <font>
@@ -2852,6 +2804,23 @@
     </dxf>
     <dxf>
       <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
@@ -2871,6 +2840,23 @@
     </dxf>
     <dxf>
       <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
@@ -2887,6 +2873,23 @@
           <bgColor auto="1"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </font>
     </dxf>
     <dxf>
       <font>
@@ -7438,22 +7441,22 @@
     <sortCondition ref="E2:E122"/>
   </sortState>
   <tableColumns count="14">
-    <tableColumn id="1" xr3:uid="{F9E01755-3C63-4F44-8496-6C8D653302C1}" uniqueName="1" name="Nachname" queryTableFieldId="1" dataDxfId="27" totalsRowDxfId="16"/>
-    <tableColumn id="2" xr3:uid="{7B6E9EB9-6FD1-674C-8E10-8F0FB6336B26}" uniqueName="2" name="Vorname" queryTableFieldId="2" dataDxfId="26" totalsRowDxfId="15"/>
-    <tableColumn id="3" xr3:uid="{7DD2E428-2048-6546-AA1D-723CC9B232ED}" uniqueName="3" name="Klasse/Information" queryTableFieldId="3" dataDxfId="25" totalsRowDxfId="14"/>
-    <tableColumn id="29" xr3:uid="{1E5A7BC0-5312-2F4D-81A1-6F2F6710FFCB}" uniqueName="29" name="Kurs-ID" queryTableFieldId="28" dataDxfId="24" totalsRowDxfId="13"/>
-    <tableColumn id="6" xr3:uid="{F813139B-1143-9241-AF76-69851F5AB246}" uniqueName="6" name="Titel" queryTableFieldId="6" dataDxfId="23" totalsRowDxfId="12"/>
-    <tableColumn id="7" xr3:uid="{D80A0002-B978-324C-8AC7-747243BFD527}" uniqueName="7" name="Beschreibung für die SuS" queryTableFieldId="7" dataDxfId="22" totalsRowDxfId="11"/>
-    <tableColumn id="8" xr3:uid="{55F4543E-1AE0-074E-9A03-3E25CA135EE3}" uniqueName="8" name="Zielstellung des iLa" queryTableFieldId="8" dataDxfId="3" totalsRowDxfId="10"/>
-    <tableColumn id="9" xr3:uid="{20B0D9D6-AB22-694A-94D8-C87C6465BAE0}" uniqueName="9" name="maximale Teilnehmerzahl" totalsRowFunction="custom" queryTableFieldId="9" dataDxfId="1" totalsRowDxfId="0">
+    <tableColumn id="1" xr3:uid="{F9E01755-3C63-4F44-8496-6C8D653302C1}" uniqueName="1" name="Nachname" queryTableFieldId="1" dataDxfId="27" totalsRowDxfId="26"/>
+    <tableColumn id="2" xr3:uid="{7B6E9EB9-6FD1-674C-8E10-8F0FB6336B26}" uniqueName="2" name="Vorname" queryTableFieldId="2" dataDxfId="25" totalsRowDxfId="24"/>
+    <tableColumn id="3" xr3:uid="{7DD2E428-2048-6546-AA1D-723CC9B232ED}" uniqueName="3" name="Klasse/Information" queryTableFieldId="3" dataDxfId="23" totalsRowDxfId="22"/>
+    <tableColumn id="29" xr3:uid="{1E5A7BC0-5312-2F4D-81A1-6F2F6710FFCB}" uniqueName="29" name="Kurs-ID" queryTableFieldId="28" dataDxfId="21" totalsRowDxfId="20"/>
+    <tableColumn id="6" xr3:uid="{F813139B-1143-9241-AF76-69851F5AB246}" uniqueName="6" name="Titel" queryTableFieldId="6" dataDxfId="19" totalsRowDxfId="18"/>
+    <tableColumn id="7" xr3:uid="{D80A0002-B978-324C-8AC7-747243BFD527}" uniqueName="7" name="Beschreibung für die SuS" queryTableFieldId="7" dataDxfId="17" totalsRowDxfId="16"/>
+    <tableColumn id="8" xr3:uid="{55F4543E-1AE0-074E-9A03-3E25CA135EE3}" uniqueName="8" name="Zielstellung des iLa" queryTableFieldId="8" dataDxfId="15" totalsRowDxfId="14"/>
+    <tableColumn id="9" xr3:uid="{20B0D9D6-AB22-694A-94D8-C87C6465BAE0}" uniqueName="9" name="maximale Teilnehmerzahl" totalsRowFunction="custom" queryTableFieldId="9" dataDxfId="13" totalsRowDxfId="0">
       <totalsRowFormula>SUM(H2:H122)</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{711711CB-1202-C946-BF85-1A7E8E0D5D5D}" uniqueName="10" name="Klassenstufen" queryTableFieldId="10" dataDxfId="2" totalsRowDxfId="4"/>
-    <tableColumn id="11" xr3:uid="{01A89DCA-B077-7045-8F6E-D98140A6C1B0}" uniqueName="11" name="Kategorie" queryTableFieldId="11" dataDxfId="21" totalsRowDxfId="9"/>
-    <tableColumn id="14" xr3:uid="{5B410BC2-38E2-D34E-8B21-763BA7E65F76}" uniqueName="14" name="Raum" queryTableFieldId="32" dataDxfId="20" totalsRowDxfId="8"/>
-    <tableColumn id="4" xr3:uid="{E57C8806-17B0-0D45-A623-70477161D4F0}" uniqueName="4" name="Wochentag" queryTableFieldId="29" dataDxfId="19" totalsRowDxfId="7"/>
-    <tableColumn id="5" xr3:uid="{6430ADEF-F650-D14F-8BA3-9C51BB510A5B}" uniqueName="5" name="Zeitschiene" queryTableFieldId="30" dataDxfId="18" totalsRowDxfId="6"/>
-    <tableColumn id="12" xr3:uid="{1F5388C9-63F0-644C-9832-768C08235AED}" uniqueName="12" name="Spalte1" queryTableFieldId="33" dataDxfId="17" totalsRowDxfId="5"/>
+    <tableColumn id="10" xr3:uid="{711711CB-1202-C946-BF85-1A7E8E0D5D5D}" uniqueName="10" name="Klassenstufen" queryTableFieldId="10" dataDxfId="12" totalsRowDxfId="11"/>
+    <tableColumn id="11" xr3:uid="{01A89DCA-B077-7045-8F6E-D98140A6C1B0}" uniqueName="11" name="Kategorie" queryTableFieldId="11" dataDxfId="10" totalsRowDxfId="9"/>
+    <tableColumn id="14" xr3:uid="{5B410BC2-38E2-D34E-8B21-763BA7E65F76}" uniqueName="14" name="Raum" queryTableFieldId="32" dataDxfId="8" totalsRowDxfId="7"/>
+    <tableColumn id="4" xr3:uid="{E57C8806-17B0-0D45-A623-70477161D4F0}" uniqueName="4" name="Wochentag" queryTableFieldId="29" dataDxfId="6" totalsRowDxfId="5"/>
+    <tableColumn id="5" xr3:uid="{6430ADEF-F650-D14F-8BA3-9C51BB510A5B}" uniqueName="5" name="Zeitschiene" queryTableFieldId="30" dataDxfId="4" totalsRowDxfId="3"/>
+    <tableColumn id="12" xr3:uid="{1F5388C9-63F0-644C-9832-768C08235AED}" uniqueName="12" name="Spalte1" queryTableFieldId="33" dataDxfId="2" totalsRowDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -7786,7 +7789,7 @@
     <col min="5" max="5" width="40.5" style="4" customWidth="1"/>
     <col min="6" max="6" width="38" style="4" customWidth="1"/>
     <col min="7" max="7" width="33.6640625" style="4" customWidth="1"/>
-    <col min="8" max="8" width="24.6640625" style="22" customWidth="1"/>
+    <col min="8" max="8" width="24.6640625" style="21" customWidth="1"/>
     <col min="9" max="9" width="15.6640625" style="6" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="23.6640625" style="4" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.33203125" style="6" bestFit="1" customWidth="1"/>
@@ -7818,7 +7821,7 @@
       <c r="G1" t="s">
         <v>393</v>
       </c>
-      <c r="H1" s="21" t="s">
+      <c r="H1" s="20" t="s">
         <v>394</v>
       </c>
       <c r="I1" s="11" t="s">
@@ -7856,7 +7859,7 @@
       <c r="E2" t="s">
         <v>239</v>
       </c>
-      <c r="H2" s="22">
+      <c r="H2" s="21">
         <v>28</v>
       </c>
       <c r="I2" s="11" t="s">
@@ -7892,7 +7895,7 @@
         <v>390</v>
       </c>
       <c r="F3"/>
-      <c r="H3" s="22">
+      <c r="H3" s="21">
         <v>28</v>
       </c>
       <c r="I3" s="11" t="s">
@@ -7933,7 +7936,7 @@
       <c r="G4" s="4" t="s">
         <v>281</v>
       </c>
-      <c r="H4" s="22">
+      <c r="H4" s="21">
         <v>10</v>
       </c>
       <c r="I4" s="6" t="s">
@@ -7977,7 +7980,7 @@
       <c r="G5" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="H5" s="23">
+      <c r="H5" s="22">
         <v>25</v>
       </c>
       <c r="I5" s="6" t="s">
@@ -8018,7 +8021,7 @@
       <c r="G6" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="H6" s="23">
+      <c r="H6" s="22">
         <v>20</v>
       </c>
       <c r="I6" s="6" t="s">
@@ -8060,7 +8063,7 @@
       <c r="G7" s="4" t="s">
         <v>379</v>
       </c>
-      <c r="H7" s="23">
+      <c r="H7" s="22">
         <v>28</v>
       </c>
       <c r="I7" s="6" t="s">
@@ -8104,10 +8107,12 @@
       <c r="G8" s="4" t="s">
         <v>183</v>
       </c>
-      <c r="H8" s="23">
+      <c r="H8" s="22">
         <v>15</v>
       </c>
-      <c r="I8" s="18"/>
+      <c r="I8" s="14" t="s">
+        <v>372</v>
+      </c>
       <c r="J8" s="4" t="s">
         <v>10</v>
       </c>
@@ -8144,7 +8149,7 @@
       <c r="G9" s="4" t="s">
         <v>181</v>
       </c>
-      <c r="H9" s="23">
+      <c r="H9" s="22">
         <v>20</v>
       </c>
       <c r="I9" s="6" t="s">
@@ -8188,7 +8193,7 @@
       <c r="G10" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="H10" s="23">
+      <c r="H10" s="22">
         <v>18</v>
       </c>
       <c r="I10" s="6" t="s">
@@ -8229,7 +8234,7 @@
       <c r="G11" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="H11" s="23">
+      <c r="H11" s="22">
         <v>20</v>
       </c>
       <c r="I11" s="6" t="s">
@@ -8270,7 +8275,7 @@
       <c r="G12" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="H12" s="23">
+      <c r="H12" s="22">
         <v>20</v>
       </c>
       <c r="I12" s="6" t="s">
@@ -8311,7 +8316,7 @@
       <c r="G13" s="4" t="s">
         <v>285</v>
       </c>
-      <c r="H13" s="23">
+      <c r="H13" s="22">
         <v>14</v>
       </c>
       <c r="I13" s="6" t="s">
@@ -8352,7 +8357,7 @@
       <c r="G14" t="s">
         <v>285</v>
       </c>
-      <c r="H14" s="24">
+      <c r="H14" s="23">
         <v>14</v>
       </c>
       <c r="I14" s="11" t="s">
@@ -8394,7 +8399,7 @@
       <c r="G15" s="4" t="s">
         <v>285</v>
       </c>
-      <c r="H15" s="23">
+      <c r="H15" s="22">
         <v>14</v>
       </c>
       <c r="I15" s="6" t="s">
@@ -8436,7 +8441,7 @@
       <c r="G16" s="4" t="s">
         <v>431</v>
       </c>
-      <c r="H16" s="23">
+      <c r="H16" s="22">
         <v>20</v>
       </c>
       <c r="I16" s="6" t="s">
@@ -8470,7 +8475,7 @@
       <c r="E17" s="4" t="s">
         <v>301</v>
       </c>
-      <c r="H17" s="23">
+      <c r="H17" s="22">
         <v>20</v>
       </c>
       <c r="I17" s="6" t="s">
@@ -8505,7 +8510,7 @@
       <c r="E18" s="4" t="s">
         <v>301</v>
       </c>
-      <c r="H18" s="23">
+      <c r="H18" s="22">
         <v>20</v>
       </c>
       <c r="I18" s="6" t="s">
@@ -8540,7 +8545,7 @@
       </c>
       <c r="F19"/>
       <c r="G19"/>
-      <c r="H19" s="24">
+      <c r="H19" s="23">
         <v>20</v>
       </c>
       <c r="I19" s="11" t="s">
@@ -8577,7 +8582,7 @@
       <c r="F20" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="H20" s="23">
+      <c r="H20" s="22">
         <v>20</v>
       </c>
       <c r="I20" s="6" t="s">
@@ -8615,7 +8620,7 @@
       <c r="F21" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="H21" s="23">
+      <c r="H21" s="22">
         <v>20</v>
       </c>
       <c r="I21" s="6" t="s">
@@ -8650,7 +8655,7 @@
       <c r="E22" s="4" t="s">
         <v>515</v>
       </c>
-      <c r="H22" s="23">
+      <c r="H22" s="22">
         <v>16</v>
       </c>
       <c r="I22" s="6" t="s">
@@ -8686,7 +8691,7 @@
       <c r="E23" s="4" t="s">
         <v>306</v>
       </c>
-      <c r="H23" s="23">
+      <c r="H23" s="22">
         <v>20</v>
       </c>
       <c r="I23" s="6" t="s">
@@ -8723,7 +8728,7 @@
       </c>
       <c r="F24"/>
       <c r="G24"/>
-      <c r="H24" s="24">
+      <c r="H24" s="23">
         <v>20</v>
       </c>
       <c r="I24" s="11" t="s">
@@ -8758,7 +8763,7 @@
       <c r="E25" s="4" t="s">
         <v>417</v>
       </c>
-      <c r="H25" s="23">
+      <c r="H25" s="22">
         <v>20</v>
       </c>
       <c r="I25" s="6" t="s">
@@ -8793,7 +8798,7 @@
       <c r="E26" s="4" t="s">
         <v>418</v>
       </c>
-      <c r="H26" s="23">
+      <c r="H26" s="22">
         <v>20</v>
       </c>
       <c r="I26" s="6" t="s">
@@ -8831,7 +8836,7 @@
       <c r="F27" s="4" t="s">
         <v>307</v>
       </c>
-      <c r="H27" s="23">
+      <c r="H27" s="22">
         <v>16</v>
       </c>
       <c r="I27" s="6" t="s">
@@ -8869,7 +8874,7 @@
       <c r="F28" s="4" t="s">
         <v>307</v>
       </c>
-      <c r="H28" s="23">
+      <c r="H28" s="22">
         <v>16</v>
       </c>
       <c r="I28" s="6" t="s">
@@ -8906,7 +8911,7 @@
       </c>
       <c r="F29"/>
       <c r="G29"/>
-      <c r="H29" s="24">
+      <c r="H29" s="23">
         <v>10</v>
       </c>
       <c r="I29" s="11" t="s">
@@ -8941,7 +8946,7 @@
       <c r="E30" s="4" t="s">
         <v>416</v>
       </c>
-      <c r="H30" s="23">
+      <c r="H30" s="22">
         <v>10</v>
       </c>
       <c r="I30" s="6" t="s">
@@ -8979,7 +8984,7 @@
       <c r="F31" s="4" t="s">
         <v>498</v>
       </c>
-      <c r="H31" s="23">
+      <c r="H31" s="22">
         <v>24</v>
       </c>
       <c r="I31" s="6" t="s">
@@ -9021,7 +9026,7 @@
       <c r="G32" s="4" t="s">
         <v>494</v>
       </c>
-      <c r="H32" s="23">
+      <c r="H32" s="22">
         <v>24</v>
       </c>
       <c r="I32" s="6" t="s">
@@ -9065,7 +9070,7 @@
       <c r="G33" s="4" t="s">
         <v>194</v>
       </c>
-      <c r="H33" s="23">
+      <c r="H33" s="22">
         <v>16</v>
       </c>
       <c r="I33" s="6" t="s">
@@ -9105,7 +9110,7 @@
       <c r="G34" t="s">
         <v>197</v>
       </c>
-      <c r="H34" s="24">
+      <c r="H34" s="23">
         <v>16</v>
       </c>
       <c r="I34" s="11" t="s">
@@ -9146,7 +9151,7 @@
       <c r="G35" s="4" t="s">
         <v>291</v>
       </c>
-      <c r="H35" s="23">
+      <c r="H35" s="22">
         <v>16</v>
       </c>
       <c r="I35" s="6" t="s">
@@ -9188,7 +9193,7 @@
       <c r="G36" s="4" t="s">
         <v>473</v>
       </c>
-      <c r="H36" s="23">
+      <c r="H36" s="22">
         <v>20</v>
       </c>
       <c r="I36" s="6" t="s">
@@ -9230,7 +9235,7 @@
       <c r="G37" s="4" t="s">
         <v>327</v>
       </c>
-      <c r="H37" s="23">
+      <c r="H37" s="22">
         <v>20</v>
       </c>
       <c r="I37" s="6" t="s">
@@ -9271,7 +9276,7 @@
       <c r="G38" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="H38" s="23">
+      <c r="H38" s="22">
         <v>24</v>
       </c>
       <c r="I38" s="6" t="s">
@@ -9313,7 +9318,7 @@
       <c r="G39" t="s">
         <v>70</v>
       </c>
-      <c r="H39" s="24">
+      <c r="H39" s="23">
         <v>18</v>
       </c>
       <c r="I39" s="11" t="s">
@@ -9354,7 +9359,7 @@
       <c r="G40" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="H40" s="23">
+      <c r="H40" s="22">
         <v>60</v>
       </c>
       <c r="I40" s="6" t="s">
@@ -9398,7 +9403,7 @@
       <c r="G41" s="4" t="s">
         <v>371</v>
       </c>
-      <c r="H41" s="23">
+      <c r="H41" s="22">
         <v>16</v>
       </c>
       <c r="I41" s="6" t="s">
@@ -9439,7 +9444,7 @@
       <c r="G42" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="H42" s="23">
+      <c r="H42" s="22">
         <v>20</v>
       </c>
       <c r="I42" s="6" t="s">
@@ -9477,7 +9482,7 @@
       <c r="F43" s="4" t="s">
         <v>512</v>
       </c>
-      <c r="H43" s="23">
+      <c r="H43" s="22">
         <v>24</v>
       </c>
       <c r="I43" s="6" t="s">
@@ -9519,7 +9524,7 @@
       <c r="G44" t="s">
         <v>452</v>
       </c>
-      <c r="H44" s="24">
+      <c r="H44" s="23">
         <v>20</v>
       </c>
       <c r="I44" s="11" t="s">
@@ -9561,7 +9566,7 @@
       <c r="G45" s="4" t="s">
         <v>452</v>
       </c>
-      <c r="H45" s="23">
+      <c r="H45" s="22">
         <v>20</v>
       </c>
       <c r="I45" s="6" t="s">
@@ -9604,7 +9609,7 @@
       <c r="G46" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="H46" s="23">
+      <c r="H46" s="22">
         <v>14</v>
       </c>
       <c r="I46" s="6" t="s">
@@ -9646,7 +9651,7 @@
       <c r="G47" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="H47" s="23">
+      <c r="H47" s="22">
         <v>14</v>
       </c>
       <c r="I47" s="6" t="s">
@@ -9688,7 +9693,7 @@
       <c r="G48" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="H48" s="23">
+      <c r="H48" s="22">
         <v>14</v>
       </c>
       <c r="I48" s="6" t="s">
@@ -9729,7 +9734,7 @@
       <c r="G49" t="s">
         <v>146</v>
       </c>
-      <c r="H49" s="24">
+      <c r="H49" s="23">
         <v>14</v>
       </c>
       <c r="I49" s="11" t="s">
@@ -9770,7 +9775,7 @@
       <c r="G50" s="4" t="s">
         <v>241</v>
       </c>
-      <c r="H50" s="23">
+      <c r="H50" s="22">
         <v>28</v>
       </c>
       <c r="I50" s="6" t="s">
@@ -9812,7 +9817,7 @@
       <c r="G51" s="4" t="s">
         <v>244</v>
       </c>
-      <c r="H51" s="23">
+      <c r="H51" s="22">
         <v>16</v>
       </c>
       <c r="I51" s="6" t="s">
@@ -9853,7 +9858,7 @@
       <c r="G52" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="H52" s="23">
+      <c r="H52" s="22">
         <v>24</v>
       </c>
       <c r="I52" s="6" t="s">
@@ -9894,7 +9899,7 @@
       <c r="G53" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="H53" s="23">
+      <c r="H53" s="22">
         <v>16</v>
       </c>
       <c r="I53" s="6" t="s">
@@ -9935,7 +9940,7 @@
       <c r="G54" t="s">
         <v>203</v>
       </c>
-      <c r="H54" s="24">
+      <c r="H54" s="23">
         <v>24</v>
       </c>
       <c r="I54" s="11" t="s">
@@ -9976,7 +9981,7 @@
       <c r="G55" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="H55" s="23">
+      <c r="H55" s="22">
         <v>18</v>
       </c>
       <c r="I55" s="6" t="s">
@@ -10017,7 +10022,7 @@
       <c r="G56" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="H56" s="23">
+      <c r="H56" s="22">
         <v>18</v>
       </c>
       <c r="I56" s="6" t="s">
@@ -10058,7 +10063,7 @@
       <c r="G57" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="H57" s="23">
+      <c r="H57" s="22">
         <v>28</v>
       </c>
       <c r="I57" s="6" t="s">
@@ -10099,7 +10104,7 @@
       <c r="G58" t="s">
         <v>153</v>
       </c>
-      <c r="H58" s="24">
+      <c r="H58" s="23">
         <v>28</v>
       </c>
       <c r="I58" s="11" t="s">
@@ -10140,7 +10145,7 @@
       <c r="G59" s="17" t="s">
         <v>531</v>
       </c>
-      <c r="H59" s="23">
+      <c r="H59" s="22">
         <v>28</v>
       </c>
       <c r="I59" s="6" t="s">
@@ -10182,7 +10187,7 @@
       <c r="G60" s="4" t="s">
         <v>448</v>
       </c>
-      <c r="H60" s="23">
+      <c r="H60" s="22">
         <v>20</v>
       </c>
       <c r="I60" s="6" t="s">
@@ -10223,7 +10228,7 @@
       <c r="G61" s="4" t="s">
         <v>168</v>
       </c>
-      <c r="H61" s="23">
+      <c r="H61" s="22">
         <v>24</v>
       </c>
       <c r="I61" s="6" t="s">
@@ -10264,7 +10269,7 @@
       <c r="G62" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="H62" s="23">
+      <c r="H62" s="22">
         <v>28</v>
       </c>
       <c r="I62" s="6" t="s">
@@ -10305,7 +10310,7 @@
       <c r="G63" t="s">
         <v>491</v>
       </c>
-      <c r="H63" s="24">
+      <c r="H63" s="23">
         <v>16</v>
       </c>
       <c r="I63" s="11">
@@ -10349,7 +10354,7 @@
       <c r="G64" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="H64" s="23">
+      <c r="H64" s="22">
         <v>18</v>
       </c>
       <c r="I64" s="6" t="s">
@@ -10396,7 +10401,7 @@
       <c r="G65" s="4" t="s">
         <v>234</v>
       </c>
-      <c r="H65" s="23">
+      <c r="H65" s="22">
         <v>20</v>
       </c>
       <c r="I65" s="6" t="s">
@@ -10443,7 +10448,7 @@
       <c r="G66" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="H66" s="23">
+      <c r="H66" s="22">
         <v>12</v>
       </c>
       <c r="I66" s="6" t="s">
@@ -10493,7 +10498,7 @@
       <c r="G67" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="H67" s="23">
+      <c r="H67" s="22">
         <v>14</v>
       </c>
       <c r="I67" s="6" t="s">
@@ -10537,7 +10542,7 @@
       <c r="G68" t="s">
         <v>172</v>
       </c>
-      <c r="H68" s="24">
+      <c r="H68" s="23">
         <v>14</v>
       </c>
       <c r="I68" s="11" t="s">
@@ -10581,7 +10586,7 @@
       <c r="G69" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="H69" s="23">
+      <c r="H69" s="22">
         <v>14</v>
       </c>
       <c r="I69" s="6" t="s">
@@ -10625,7 +10630,7 @@
       <c r="G70" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="H70" s="23">
+      <c r="H70" s="22">
         <v>15</v>
       </c>
       <c r="I70" s="6" t="s">
@@ -10666,7 +10671,7 @@
       <c r="G71" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="H71" s="23">
+      <c r="H71" s="22">
         <v>24</v>
       </c>
       <c r="I71" s="6" t="s">
@@ -10707,7 +10712,7 @@
       <c r="G72" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="H72" s="23">
+      <c r="H72" s="22">
         <v>24</v>
       </c>
       <c r="I72" s="6" t="s">
@@ -10748,7 +10753,7 @@
       <c r="G73" t="s">
         <v>129</v>
       </c>
-      <c r="H73" s="24">
+      <c r="H73" s="23">
         <v>24</v>
       </c>
       <c r="I73" s="11" t="s">
@@ -10789,7 +10794,7 @@
       <c r="G74" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="H74" s="23">
+      <c r="H74" s="22">
         <v>28</v>
       </c>
       <c r="I74" s="6" t="s">
@@ -10830,7 +10835,7 @@
       <c r="G75" s="4" t="s">
         <v>478</v>
       </c>
-      <c r="H75" s="23">
+      <c r="H75" s="22">
         <v>14</v>
       </c>
       <c r="I75" s="6" t="s">
@@ -10872,7 +10877,7 @@
       <c r="G76" s="4" t="s">
         <v>384</v>
       </c>
-      <c r="H76" s="23">
+      <c r="H76" s="22">
         <v>20</v>
       </c>
       <c r="I76" s="6" t="s">
@@ -10910,7 +10915,7 @@
       <c r="F77" s="4" t="s">
         <v>433</v>
       </c>
-      <c r="H77" s="23">
+      <c r="H77" s="22">
         <v>20</v>
       </c>
       <c r="I77" s="6" t="s">
@@ -10946,7 +10951,7 @@
         <v>510</v>
       </c>
       <c r="G78"/>
-      <c r="H78" s="24">
+      <c r="H78" s="23">
         <v>18</v>
       </c>
       <c r="I78" s="11" t="s">
@@ -10980,7 +10985,7 @@
       <c r="F79" s="4" t="s">
         <v>508</v>
       </c>
-      <c r="H79" s="23">
+      <c r="H79" s="22">
         <v>18</v>
       </c>
       <c r="I79" s="6" t="s">
@@ -11020,7 +11025,7 @@
       <c r="G80" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="H80" s="23">
+      <c r="H80" s="22">
         <v>18</v>
       </c>
       <c r="I80" s="6" t="s">
@@ -11061,7 +11066,7 @@
       <c r="G81" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="H81" s="23">
+      <c r="H81" s="22">
         <v>18</v>
       </c>
       <c r="I81" s="6" t="s">
@@ -11102,7 +11107,7 @@
       <c r="G82" s="4" t="s">
         <v>455</v>
       </c>
-      <c r="H82" s="23">
+      <c r="H82" s="22">
         <v>24</v>
       </c>
       <c r="I82" s="6" t="s">
@@ -11144,7 +11149,7 @@
       <c r="G83" t="s">
         <v>458</v>
       </c>
-      <c r="H83" s="24">
+      <c r="H83" s="23">
         <v>30</v>
       </c>
       <c r="I83" s="11" t="s">
@@ -11186,7 +11191,7 @@
       <c r="G84" s="4" t="s">
         <v>189</v>
       </c>
-      <c r="H84" s="23">
+      <c r="H84" s="22">
         <v>18</v>
       </c>
       <c r="I84" s="6" t="s">
@@ -11227,7 +11232,7 @@
       <c r="G85" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="H85" s="23">
+      <c r="H85" s="22">
         <v>15</v>
       </c>
       <c r="I85" s="6">
@@ -11269,7 +11274,7 @@
       <c r="G86" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="H86" s="23">
+      <c r="H86" s="22">
         <v>15</v>
       </c>
       <c r="I86" s="6">
@@ -11311,7 +11316,7 @@
       <c r="G87" s="4" t="s">
         <v>481</v>
       </c>
-      <c r="H87" s="23">
+      <c r="H87" s="22">
         <v>20</v>
       </c>
       <c r="I87" s="6" t="s">
@@ -11355,7 +11360,7 @@
       <c r="G88" t="s">
         <v>467</v>
       </c>
-      <c r="H88" s="24">
+      <c r="H88" s="23">
         <v>20</v>
       </c>
       <c r="I88" s="11" t="s">
@@ -11396,7 +11401,7 @@
       <c r="G89" s="4" t="s">
         <v>464</v>
       </c>
-      <c r="H89" s="23">
+      <c r="H89" s="22">
         <v>20</v>
       </c>
       <c r="I89" s="6" t="s">
@@ -11440,7 +11445,7 @@
       <c r="G90" s="4" t="s">
         <v>462</v>
       </c>
-      <c r="H90" s="23">
+      <c r="H90" s="22">
         <v>20</v>
       </c>
       <c r="I90" s="6" t="s">
@@ -11481,7 +11486,7 @@
       <c r="G91" s="4" t="s">
         <v>266</v>
       </c>
-      <c r="H91" s="23">
+      <c r="H91" s="22">
         <v>18</v>
       </c>
       <c r="I91" s="6" t="s">
@@ -11522,7 +11527,7 @@
       <c r="G92" s="4" t="s">
         <v>262</v>
       </c>
-      <c r="H92" s="23">
+      <c r="H92" s="22">
         <v>7</v>
       </c>
       <c r="I92" s="6" t="s">
@@ -11562,11 +11567,11 @@
       </c>
       <c r="F93"/>
       <c r="G93"/>
-      <c r="H93" s="24">
+      <c r="H93" s="23">
         <v>24</v>
       </c>
-      <c r="I93" s="11">
-        <v>5.6</v>
+      <c r="I93" s="11" t="s">
+        <v>40</v>
       </c>
       <c r="J93" t="s">
         <v>18</v>
@@ -11600,7 +11605,7 @@
       <c r="F94" s="4" t="s">
         <v>314</v>
       </c>
-      <c r="H94" s="23">
+      <c r="H94" s="22">
         <v>20</v>
       </c>
       <c r="I94" s="6" t="s">
@@ -11641,7 +11646,7 @@
       <c r="G95" s="4" t="s">
         <v>376</v>
       </c>
-      <c r="H95" s="23">
+      <c r="H95" s="22">
         <v>20</v>
       </c>
       <c r="I95" s="6" t="s">
@@ -11682,7 +11687,7 @@
       <c r="G96" s="4" t="s">
         <v>215</v>
       </c>
-      <c r="H96" s="23">
+      <c r="H96" s="22">
         <v>15</v>
       </c>
       <c r="I96" s="6" t="s">
@@ -11724,7 +11729,7 @@
       <c r="G97" s="4" t="s">
         <v>215</v>
       </c>
-      <c r="H97" s="23">
+      <c r="H97" s="22">
         <v>15</v>
       </c>
       <c r="I97" s="6" t="s">
@@ -11766,7 +11771,7 @@
       <c r="G98" t="s">
         <v>297</v>
       </c>
-      <c r="H98" s="24">
+      <c r="H98" s="23">
         <v>24</v>
       </c>
       <c r="I98" s="11" t="s">
@@ -11807,7 +11812,7 @@
       <c r="G99" s="4" t="s">
         <v>297</v>
       </c>
-      <c r="H99" s="23">
+      <c r="H99" s="22">
         <v>24</v>
       </c>
       <c r="I99" s="6" t="s">
@@ -11842,7 +11847,7 @@
       <c r="E100" s="4" t="s">
         <v>368</v>
       </c>
-      <c r="H100" s="23">
+      <c r="H100" s="22">
         <v>24</v>
       </c>
       <c r="I100" s="6" t="s">
@@ -11883,7 +11888,7 @@
       <c r="G101" s="4" t="s">
         <v>272</v>
       </c>
-      <c r="H101" s="23">
+      <c r="H101" s="22">
         <v>14</v>
       </c>
       <c r="I101" s="6" t="s">
@@ -11924,7 +11929,7 @@
       <c r="G102" s="4" t="s">
         <v>272</v>
       </c>
-      <c r="H102" s="23">
+      <c r="H102" s="22">
         <v>14</v>
       </c>
       <c r="I102" s="6" t="s">
@@ -11965,7 +11970,7 @@
       <c r="G103" t="s">
         <v>275</v>
       </c>
-      <c r="H103" s="24">
+      <c r="H103" s="23">
         <v>26</v>
       </c>
       <c r="I103" s="11" t="s">
@@ -12006,7 +12011,7 @@
       <c r="G104" s="4" t="s">
         <v>251</v>
       </c>
-      <c r="H104" s="23">
+      <c r="H104" s="22">
         <v>16</v>
       </c>
       <c r="I104" s="6" t="s">
@@ -12042,7 +12047,7 @@
       <c r="E105" s="4" t="s">
         <v>368</v>
       </c>
-      <c r="H105" s="23">
+      <c r="H105" s="22">
         <v>24</v>
       </c>
       <c r="I105" s="6" t="s">
@@ -12082,7 +12087,7 @@
       <c r="G106" s="4" t="s">
         <v>445</v>
       </c>
-      <c r="H106" s="23">
+      <c r="H106" s="22">
         <v>15</v>
       </c>
       <c r="I106" s="6" t="s">
@@ -12121,7 +12126,7 @@
       <c r="G107" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="H107" s="23">
+      <c r="H107" s="22">
         <v>12</v>
       </c>
       <c r="I107" s="6" t="s">
@@ -12165,7 +12170,7 @@
       <c r="G108" t="s">
         <v>93</v>
       </c>
-      <c r="H108" s="24">
+      <c r="H108" s="23">
         <v>15</v>
       </c>
       <c r="I108" s="11" t="s">
@@ -12206,7 +12211,7 @@
       <c r="G109" s="4" t="s">
         <v>257</v>
       </c>
-      <c r="H109" s="23">
+      <c r="H109" s="22">
         <v>28</v>
       </c>
       <c r="I109" s="6" t="s">
@@ -12248,7 +12253,7 @@
       <c r="G110" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="H110" s="23">
+      <c r="H110" s="22">
         <v>24</v>
       </c>
       <c r="I110" s="6" t="s">
@@ -12290,7 +12295,7 @@
       <c r="G111" s="4" t="s">
         <v>501</v>
       </c>
-      <c r="H111" s="23">
+      <c r="H111" s="22">
         <v>24</v>
       </c>
       <c r="I111" s="6" t="s">
@@ -12331,7 +12336,7 @@
       <c r="G112" s="4" t="s">
         <v>501</v>
       </c>
-      <c r="H112" s="23">
+      <c r="H112" s="22">
         <v>24</v>
       </c>
       <c r="I112" s="6" t="s">
@@ -12372,7 +12377,7 @@
       <c r="G113" t="s">
         <v>208</v>
       </c>
-      <c r="H113" s="24">
+      <c r="H113" s="23">
         <v>14</v>
       </c>
       <c r="I113" s="11" t="s">
@@ -12413,7 +12418,7 @@
       <c r="G114" s="4" t="s">
         <v>208</v>
       </c>
-      <c r="H114" s="23">
+      <c r="H114" s="22">
         <v>14</v>
       </c>
       <c r="I114" s="6" t="s">
@@ -12454,7 +12459,7 @@
       <c r="G115" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="H115" s="23">
+      <c r="H115" s="22">
         <v>28</v>
       </c>
       <c r="I115" s="6" t="s">
@@ -12496,7 +12501,7 @@
       <c r="G116" s="4" t="s">
         <v>438</v>
       </c>
-      <c r="H116" s="23">
+      <c r="H116" s="22">
         <v>28</v>
       </c>
       <c r="I116" s="6" t="s">
@@ -12538,7 +12543,7 @@
       <c r="G117" s="4" t="s">
         <v>441</v>
       </c>
-      <c r="H117" s="23">
+      <c r="H117" s="22">
         <v>14</v>
       </c>
       <c r="I117" s="6" t="s">
@@ -12579,7 +12584,7 @@
       <c r="G118" t="s">
         <v>488</v>
       </c>
-      <c r="H118" s="24">
+      <c r="H118" s="23">
         <v>15</v>
       </c>
       <c r="I118" s="11" t="s">
@@ -12620,7 +12625,7 @@
       <c r="G119" s="4" t="s">
         <v>485</v>
       </c>
-      <c r="H119" s="23">
+      <c r="H119" s="22">
         <v>20</v>
       </c>
       <c r="I119" s="6">
@@ -12661,11 +12666,11 @@
       <c r="G120" s="4" t="s">
         <v>228</v>
       </c>
-      <c r="H120" s="23">
+      <c r="H120" s="22">
         <v>16</v>
       </c>
-      <c r="I120" s="6">
-        <v>6.7</v>
+      <c r="I120" s="24" t="s">
+        <v>659</v>
       </c>
       <c r="J120" s="4" t="s">
         <v>10</v>
@@ -12696,10 +12701,10 @@
       <c r="E121" s="4" t="s">
         <v>333</v>
       </c>
-      <c r="F121" s="20" t="s">
+      <c r="F121" t="s">
         <v>658</v>
       </c>
-      <c r="H121" s="23">
+      <c r="H121" s="22">
         <v>20</v>
       </c>
       <c r="I121" s="6" t="s">
@@ -12719,8 +12724,12 @@
       </c>
     </row>
     <row r="122" spans="1:14" ht="15" customHeight="1">
-      <c r="A122"/>
-      <c r="B122"/>
+      <c r="A122" s="4" t="s">
+        <v>330</v>
+      </c>
+      <c r="B122" s="4" t="s">
+        <v>331</v>
+      </c>
       <c r="C122"/>
       <c r="D122" s="15" t="s">
         <v>656</v>
@@ -12734,7 +12743,7 @@
       <c r="G122" s="4" t="s">
         <v>360</v>
       </c>
-      <c r="H122" s="23">
+      <c r="H122" s="22">
         <v>19</v>
       </c>
       <c r="I122" s="6" t="s">
@@ -12754,7 +12763,7 @@
       </c>
     </row>
     <row r="123" spans="1:14">
-      <c r="H123" s="22">
+      <c r="H123" s="21">
         <f>SUM(H2:H122)</f>
         <v>2382</v>
       </c>
@@ -12762,7 +12771,7 @@
     </row>
     <row r="124" spans="1:14">
       <c r="D124" s="8"/>
-      <c r="H124" s="22">
+      <c r="H124" s="21">
         <f>SUMIF(H2:H122,"Donnerstag",L2:L122)</f>
         <v>0</v>
       </c>
